--- a/data/trans_bre/IP2004-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,45</t>
+          <t>0,0; 8,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 1,4</t>
+          <t>-15,65; 0,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 10,77</t>
+          <t>-5,0; 10,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 0,0</t>
+          <t>-4,24; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,35; 78,5</t>
+          <t>-93,37; 50,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 541,97</t>
+          <t>-75,37; 707,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 6,8</t>
+          <t>-8,66; 6,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,25</t>
+          <t>-3,64; 4,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,68</t>
+          <t>-4,15; 0,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,7</t>
+          <t>-1,49; 0,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 73,37</t>
+          <t>-49,3; 70,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,24</t>
+          <t>-1,58; 4,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 8,71</t>
+          <t>-0,97; 9,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 10,67</t>
+          <t>-0,87; 9,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 0,04</t>
+          <t>-11,22; 0,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,17</t>
+          <t>0,0; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 7,42</t>
+          <t>-0,96; 7,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 13,84</t>
+          <t>-1,09; 13,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 5,79</t>
+          <t>-4,49; 5,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 729,72</t>
+          <t>-30,03; 801,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 12,3</t>
+          <t>-1,33; 12,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 13,0</t>
+          <t>-7,09; 13,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 0,0</t>
+          <t>-7,31; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 5,06</t>
+          <t>-2,65; 6,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-69,08; 357,84</t>
+          <t>-69,56; 372,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 3,33</t>
+          <t>-4,29; 3,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,6</t>
+          <t>-3,08; 5,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,0</t>
+          <t>-4,44; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 5,51</t>
+          <t>-0,71; 5,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,32</t>
+          <t>-0,59; 3,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 2,14</t>
+          <t>-6,34; 2,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,03; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-83,6; 102,36</t>
+          <t>-80,81; 116,43</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,59</t>
+          <t>-2,2; 3,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,48</t>
+          <t>-1,51; 2,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,0</t>
+          <t>-4,04; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,81; 431,1</t>
+          <t>-70,18; 324,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,86</t>
+          <t>-1,32; 1,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,15</t>
+          <t>-1,01; 2,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,59</t>
+          <t>-0,03; 2,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,12</t>
+          <t>-2,31; 0,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 78,06</t>
+          <t>-35,41; 73,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 113,67</t>
+          <t>-32,31; 126,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 229,47</t>
+          <t>-4,7; 229,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-78,1; 14,18</t>
+          <t>-77,8; 12,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,99</t>
+          <t>0,0; 8,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 0,76</t>
+          <t>-15,61; 0,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 10,83</t>
+          <t>-4,27; 9,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,0</t>
+          <t>-4,48; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,37; 50,73</t>
+          <t>-100,0; 26,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-75,37; 707,56</t>
+          <t>-65,55; 601,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 6,28</t>
+          <t>-8,96; 6,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 4,15</t>
+          <t>-3,69; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,7</t>
+          <t>-4,61; 0,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,93</t>
+          <t>-1,45; 0,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 70,05</t>
+          <t>-51,41; 71,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,22</t>
+          <t>-1,59; 3,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 9,4</t>
+          <t>-0,44; 9,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 9,52</t>
+          <t>-0,83; 10,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 0,18</t>
+          <t>-12,31; -0,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,55</t>
+          <t>0,0; 7,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 7,44</t>
+          <t>-0,87; 7,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 13,96</t>
+          <t>-0,92; 12,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 5,74</t>
+          <t>-4,06; 6,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 801,62</t>
+          <t>-31,42; 654,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 12,3</t>
+          <t>-1,5; 11,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 13,96</t>
+          <t>-7,62; 13,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 0,0</t>
+          <t>-7,66; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 6,47</t>
+          <t>-2,7; 5,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 372,65</t>
+          <t>-73,08; 354,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,18</t>
+          <t>-4,31; 4,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 5,55</t>
+          <t>-3,03; 6,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,0</t>
+          <t>-3,36; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 5,76</t>
+          <t>-0,8; 5,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,42</t>
+          <t>-0,64; 3,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 2,43</t>
+          <t>-5,97; 2,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-74,03; —</t>
+          <t>-69,34; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-80,81; 116,43</t>
+          <t>-79,14; 93,49</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,44</t>
+          <t>-2,23; 3,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,54</t>
+          <t>-1,56; 2,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,0</t>
+          <t>-4,42; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-70,18; 324,8</t>
+          <t>-65,77; 355,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,82</t>
+          <t>-1,21; 1,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,26</t>
+          <t>-0,82; 2,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,56</t>
+          <t>-0,11; 2,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,07</t>
+          <t>-2,39; 0,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 73,28</t>
+          <t>-33,81; 71,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 126,16</t>
+          <t>-24,56; 129,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 229,02</t>
+          <t>-8,03; 252,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-77,8; 12,29</t>
+          <t>-77,15; 24,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2004-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2004-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,73</t>
+          <t>0,0; 9,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 0,8</t>
+          <t>-15,01; 1,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 9,91</t>
+          <t>-4,23; 10,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,0</t>
+          <t>-3,83; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,96</t>
+          <t>-93,35; 78,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-65,55; 601,87</t>
+          <t>-68,28; 541,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-46,93%</t>
+          <t>-30,16%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 6,85</t>
+          <t>-8,74; 6,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,95</t>
+          <t>-3,05; 4,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,7</t>
+          <t>-4,17; 0,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,97</t>
+          <t>-1,09; 0,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 71,69</t>
+          <t>-51,25; 73,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,11</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-79,84%</t>
+          <t>-73,38%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,47</t>
+          <t>-1,58; 4,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 9,81</t>
+          <t>-0,88; 8,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 10,74</t>
+          <t>-0,82; 10,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -0,14</t>
+          <t>-7,72; 1,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,3</t>
+          <t>0,0; 7,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 7,74</t>
+          <t>-0,73; 7,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 12,46</t>
+          <t>-0,8; 13,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 6,08</t>
+          <t>-4,14; 6,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 654,74</t>
+          <t>-26,09; 729,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 11,81</t>
+          <t>-1,5; 12,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 13,48</t>
+          <t>-7,82; 13,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 0,0</t>
+          <t>-7,2; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 5,21</t>
+          <t>-3,03; 5,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-73,08; 354,33</t>
+          <t>-69,08; 357,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 4,12</t>
+          <t>-4,47; 3,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 6,73</t>
+          <t>-3,15; 5,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>-2,42</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-36,78%</t>
+          <t>-40,16%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,0</t>
+          <t>-3,91; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,89</t>
+          <t>-0,88; 5,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,37</t>
+          <t>-0,6; 3,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 2,54</t>
+          <t>-7,7; 1,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-69,34; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-79,14; 93,49</t>
+          <t>-85,68; 80,36</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,25</t>
+          <t>-2,34; 3,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,51</t>
+          <t>-1,57; 2,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 0,0</t>
+          <t>-4,16; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 355,34</t>
+          <t>-69,81; 431,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-48,9%</t>
+          <t>-43,49%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,8</t>
+          <t>-1,33; 1,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,32</t>
+          <t>-0,77; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,65</t>
+          <t>-0,18; 2,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,18</t>
+          <t>-2,28; 0,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 71,87</t>
+          <t>-34,82; 78,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 129,53</t>
+          <t>-27,86; 113,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 252,36</t>
+          <t>-13,18; 229,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-77,15; 24,01</t>
+          <t>-76,07; 24,91</t>
         </is>
       </c>
     </row>
